--- a/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
+++ b/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
@@ -3086,7 +3086,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>di-Methylation</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>

--- a/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
+++ b/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
@@ -3086,7 +3086,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>di-Methylation</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>Ethylation</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>

--- a/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
+++ b/Dependencies/Ping_2018/PTM_heatmap_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5039</v>
+        <v>5069</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -806,7 +806,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dihydroxy</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>528</v>
+        <v>440</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -882,7 +882,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>328</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Iodoacetic acid derivative</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>dihydroxy</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>546</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 3 protons by iron</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by calcium</t>
+          <t>Replacement of 3 protons by iron</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Replacement of 2 protons by calcium</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>replacement of proton with ammonium ion</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Addition of Glycine</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>quinone</t>
+          <t>Addition of Glycine</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Nterm_mono</t>
+          <t>quinone</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>glyoxal-derived AGE</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>cysteine oxidation to cysteic acid</t>
+          <t>glyoxal-derived AGE</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Acetylation</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>fluorination</t>
+          <t>cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Replacement of proton by potassium</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton by potassium</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>fluorination</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>persulfide</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hydroxymethyl</t>
+          <t>Missing TMT10_Lys_mono</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Beta-methylthiolation</t>
+          <t>persulfide</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>di-Methylation</t>
+          <t>carboxyethyl</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3162,7 +3162,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Ethylation</t>
+          <t>hydroxymethyl</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3238,76 +3238,456 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>Beta-methylthiolation</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Missing TMT10_Nterm_mono</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Ethylation</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>di-Methylation</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
           <t>Phosphorylation</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
         <v>0</v>
       </c>
     </row>
